--- a/data/Tender_Organisations.xlsx
+++ b/data/Tender_Organisations.xlsx
@@ -578,12 +578,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>受阻</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[2026-07-09 12:30] 🔒 網站防爬蟲攔截 (403)，已加入綜合報告提示手動檢查</t>
+          <t>2026-09-14 健康檢查:HTTP 200,由受阻升正常</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>受阻</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[2026-07-09 12:31] 🔒 網站防爬蟲攔截 (403)，已加入綜合報告提示手動檢查</t>
+          <t>2026-09-14 健康檢查:HTTP 200,由受阻升正常</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>受阻</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>[2026-07-14] 新增機構,待首次掃描</t>
+          <t>2026-09-14 健康檢查:HTTP 200,由受阻升正常</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
